--- a/Employee Data/Medical_Bills.xlsx
+++ b/Employee Data/Medical_Bills.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\servadmin\Desktop\Saudi Ic\Employee Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669E9EBB-FD85-4F36-963C-4DE8892A2813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10820A4-60CE-4D5B-8FAE-1EE5F2E0C234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="300" windowWidth="20100" windowHeight="11508" xr2:uid="{66CB86FE-BFDD-7049-97E8-48DD3887B9E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66CB86FE-BFDD-7049-97E8-48DD3887B9E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>S.No</t>
   </si>
@@ -51,97 +51,25 @@
     <t>Red Sea HC-02, HC-03 Bills</t>
   </si>
   <si>
-    <t>Abdelghani Ohzza</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amount(SAR) </t>
-  </si>
-  <si>
-    <t>Abdullha</t>
-  </si>
-  <si>
-    <t>Fever Medical Bill</t>
-  </si>
-  <si>
-    <t>said dendoum</t>
-  </si>
-  <si>
-    <t>Eye issue</t>
-  </si>
-  <si>
-    <t>Inamul Haq</t>
-  </si>
-  <si>
-    <t>Pain</t>
-  </si>
-  <si>
-    <t>idir aitba</t>
   </si>
   <si>
     <t>invoice no</t>
   </si>
   <si>
-    <t>mustafa</t>
-  </si>
-  <si>
-    <t>liver infection</t>
-  </si>
-  <si>
-    <t>Haq nawaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skin Infection </t>
-  </si>
-  <si>
     <t>Shakir</t>
-  </si>
-  <si>
-    <t>Cough</t>
-  </si>
-  <si>
-    <t>Ram Krit</t>
-  </si>
-  <si>
-    <t>Infection</t>
-  </si>
-  <si>
-    <t>Sabir</t>
-  </si>
-  <si>
-    <t>Sanjay</t>
-  </si>
-  <si>
-    <t>sajjad</t>
-  </si>
-  <si>
-    <t>shuaib</t>
-  </si>
-  <si>
-    <t>PileslKedney infection</t>
-  </si>
-  <si>
-    <t>Shamshad</t>
-  </si>
-  <si>
-    <t>hani</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>HeartEcg</t>
+    <t>Nasir</t>
   </si>
   <si>
-    <t>Amir Driver</t>
+    <t>this bill not coverd by hospital EIV fluid( FEVER)</t>
   </si>
   <si>
-    <t>Liver problem</t>
-  </si>
-  <si>
-    <t>Harun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In ramzan iftar part fall down due to vertigo injured </t>
+    <t>Slip in room, injured, this bill not coverd by insurance</t>
   </si>
 </sst>
 </file>
@@ -315,6 +243,16 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -324,21 +262,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,15 +594,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -687,409 +615,251 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="18"/>
+        <v>6</v>
+      </c>
+      <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>4703</v>
+        <v>2162</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F3" s="8">
-        <v>460281</v>
-      </c>
-      <c r="G3" s="8">
-        <v>16278</v>
-      </c>
-      <c r="H3" s="18"/>
+        <v>532428</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>3276</v>
+        <v>3146</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" s="8">
-        <v>202201</v>
+        <v>532423</v>
       </c>
       <c r="G4" s="8"/>
-      <c r="H4" s="18"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
-        <v>4495</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2">
-        <v>115</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="8">
-        <v>203793</v>
-      </c>
-      <c r="G5" s="10">
-        <v>25232</v>
-      </c>
-      <c r="H5" s="19"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="14"/>
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
-        <v>2806</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2">
-        <v>106</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="8">
-        <v>907400100027330</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="18"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
-        <v>4071</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="2">
-        <v>138</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="8">
-        <v>26397</v>
-      </c>
-      <c r="G7" s="8">
-        <v>204359</v>
-      </c>
-      <c r="H7" s="18"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
-        <v>4212</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2">
-        <v>211</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1318878</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="18"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
-        <v>1619</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2">
-        <v>105</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="8">
-        <v>907400100030298</v>
-      </c>
-      <c r="G9" s="10">
-        <v>907400100018275</v>
-      </c>
-      <c r="H9" s="18"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
-        <v>3146</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="2">
-        <v>42</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="8">
-        <v>517462</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="18"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
-        <v>3361</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="2">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="8">
-        <v>200759</v>
-      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="18"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>3016</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2">
-        <v>42</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="8">
-        <v>517460</v>
-      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="18"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
-        <v>3085</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="2">
-        <v>79</v>
-      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="8">
-        <v>906700100027176</v>
-      </c>
+      <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="18"/>
+      <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
-        <v>4158</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2">
-        <v>16</v>
-      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="8">
-        <v>200751</v>
-      </c>
+      <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="18"/>
+      <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
-        <v>2008</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="2">
-        <v>79</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="8">
-        <v>204474</v>
-      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="18"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
-        <v>2906</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="2">
-        <v>70</v>
-      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="8">
-        <v>517464</v>
-      </c>
+      <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="18"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
-        <v>3394</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="2">
-        <v>117</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="8">
-        <v>204698</v>
-      </c>
-      <c r="G17" s="8">
-        <v>27292</v>
-      </c>
-      <c r="H17" s="18"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="13"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15">
-        <v>3849</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="15">
-        <v>360</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="8">
-        <v>44914</v>
-      </c>
-      <c r="G18" s="8">
-        <v>184133</v>
-      </c>
-      <c r="H18" s="19">
-        <v>67933</v>
-      </c>
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="14"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15">
-        <v>4162</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="15">
-        <v>100</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="8">
-        <v>5108050</v>
-      </c>
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="18"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>51</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="11"/>
+      <c r="B20" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="15"/>
       <c r="D20" s="7">
         <f>SUM(D3:D19)</f>
-        <v>1854</v>
+        <v>140</v>
       </c>
       <c r="E20" s="1"/>
     </row>

--- a/Employee Data/Medical_Bills.xlsx
+++ b/Employee Data/Medical_Bills.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\servadmin\Desktop\Saudi Ic\Employee Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10820A4-60CE-4D5B-8FAE-1EE5F2E0C234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F78F468-30CF-4918-9A9F-7A3AA18B44F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66CB86FE-BFDD-7049-97E8-48DD3887B9E1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>S.No</t>
   </si>
@@ -70,6 +70,30 @@
   </si>
   <si>
     <t>Slip in room, injured, this bill not coverd by insurance</t>
+  </si>
+  <si>
+    <t>Munna</t>
+  </si>
+  <si>
+    <t>Fever</t>
+  </si>
+  <si>
+    <t>Sajid</t>
+  </si>
+  <si>
+    <t>Krishna bista</t>
+  </si>
+  <si>
+    <t>hachibul molla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bone of the hand issue during work </t>
+  </si>
+  <si>
+    <t>C-64119</t>
+  </si>
+  <si>
+    <t>C-64124</t>
   </si>
 </sst>
 </file>
@@ -676,11 +700,21 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="8"/>
+      <c r="B5" s="2">
+        <v>4276</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8">
+        <v>220894</v>
+      </c>
       <c r="G5" s="10"/>
       <c r="H5" s="14"/>
       <c r="I5" s="6"/>
@@ -689,11 +723,21 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="8"/>
+      <c r="B6" s="2">
+        <v>3086</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2">
+        <v>49</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8">
+        <v>216954</v>
+      </c>
       <c r="G6" s="8"/>
       <c r="H6" s="13"/>
     </row>
@@ -701,11 +745,21 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="8"/>
+      <c r="B7" s="2">
+        <v>3183</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2">
+        <v>70</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="8">
+        <v>537004</v>
+      </c>
       <c r="G7" s="8"/>
       <c r="H7" s="13"/>
     </row>
@@ -713,11 +767,21 @@
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="8"/>
+      <c r="B8" s="2">
+        <v>4273</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2">
+        <v>67</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="G8" s="8"/>
       <c r="H8" s="13"/>
     </row>
@@ -725,11 +789,21 @@
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="8"/>
+      <c r="B9" s="2">
+        <v>4273</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2">
+        <v>138</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="8">
+        <v>222662</v>
+      </c>
       <c r="G9" s="10"/>
       <c r="H9" s="13"/>
     </row>
@@ -737,11 +811,21 @@
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="8"/>
+      <c r="B10" s="2">
+        <v>4273</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2">
+        <v>92</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="G10" s="8"/>
       <c r="H10" s="13"/>
     </row>
@@ -859,7 +943,7 @@
       <c r="C20" s="15"/>
       <c r="D20" s="7">
         <f>SUM(D3:D19)</f>
-        <v>140</v>
+        <v>586</v>
       </c>
       <c r="E20" s="1"/>
     </row>
